--- a/research/traditional_assets/database/data/qatar/qatar_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0344</v>
+        <v>0.0332</v>
       </c>
       <c r="E2">
-        <v>0.0175</v>
+        <v>0.0318</v>
       </c>
       <c r="F2">
-        <v>0.1095</v>
+        <v>0.138</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0002669206888484705</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.0002630441821930483</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>6365.900000000001</v>
+        <v>6625</v>
       </c>
       <c r="L2">
-        <v>0.5885469153037546</v>
+        <v>0.5404016509780251</v>
       </c>
       <c r="M2">
-        <v>2588</v>
+        <v>3165.7</v>
       </c>
       <c r="N2">
-        <v>0.02825654497136131</v>
+        <v>0.03948635433817293</v>
       </c>
       <c r="O2">
-        <v>0.4065411018080711</v>
+        <v>0.4778415094339623</v>
       </c>
       <c r="P2">
-        <v>2588</v>
+        <v>3165.7</v>
       </c>
       <c r="Q2">
-        <v>0.02825654497136131</v>
+        <v>0.03948635433817293</v>
       </c>
       <c r="R2">
-        <v>0.4065411018080711</v>
+        <v>0.4778415094339623</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,67 +639,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>41179.7</v>
+        <v>48484.1</v>
       </c>
       <c r="V2">
-        <v>0.4496120730128158</v>
+        <v>0.6047510352741605</v>
       </c>
       <c r="W2">
-        <v>0.1208309341365106</v>
+        <v>0.1003092385001933</v>
       </c>
       <c r="X2">
-        <v>0.06464429774474004</v>
+        <v>0.1040603538562386</v>
       </c>
       <c r="Y2">
-        <v>0.05618663639177059</v>
+        <v>-0.003751115356045359</v>
       </c>
       <c r="Z2">
-        <v>0.1209491184886088</v>
+        <v>0.1228450953749464</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04735693592630231</v>
+        <v>0.07379383517399402</v>
       </c>
       <c r="AC2">
-        <v>-0.04735693592630231</v>
+        <v>-0.07379383517399402</v>
       </c>
       <c r="AD2">
-        <v>87570.5</v>
+        <v>99618.5</v>
       </c>
       <c r="AE2">
-        <v>22.91452876604144</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>87593.41452876604</v>
+        <v>99618.5</v>
       </c>
       <c r="AG2">
-        <v>46413.71452876604</v>
+        <v>51134.4</v>
       </c>
       <c r="AH2">
-        <v>0.4888494176136729</v>
+        <v>0.5540809998303581</v>
       </c>
       <c r="AI2">
-        <v>0.6187980817114693</v>
+        <v>0.6301737716740152</v>
       </c>
       <c r="AJ2">
-        <v>0.3363236741957105</v>
+        <v>0.3894280857597193</v>
       </c>
       <c r="AK2">
-        <v>0.4624058306757491</v>
+        <v>0.4665679412465134</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>11722.95850066935</v>
-      </c>
-      <c r="AP2">
-        <v>6213.34866516279</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0634</v>
+        <v>0.0423</v>
       </c>
       <c r="E3">
-        <v>0.0457</v>
+        <v>0.0542</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,28 +731,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>272.8</v>
+        <v>292.7</v>
       </c>
       <c r="L3">
-        <v>0.461590524534687</v>
+        <v>0.4988070892978869</v>
       </c>
       <c r="M3">
-        <v>172.8</v>
+        <v>180.8</v>
       </c>
       <c r="N3">
-        <v>0.04512456259466235</v>
+        <v>0.04181120207205958</v>
       </c>
       <c r="O3">
-        <v>0.6334310850439883</v>
+        <v>0.6176973009907756</v>
       </c>
       <c r="P3">
-        <v>172.8</v>
+        <v>180.8</v>
       </c>
       <c r="Q3">
-        <v>0.04512456259466235</v>
+        <v>0.04181120207205958</v>
       </c>
       <c r="R3">
-        <v>0.6334310850439883</v>
+        <v>0.6176973009907756</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1098</v>
+        <v>1084.2</v>
       </c>
       <c r="V3">
-        <v>0.286728991486917</v>
+        <v>0.2507284584431803</v>
       </c>
       <c r="W3">
-        <v>0.1208309341365106</v>
+        <v>0.1244314075585597</v>
       </c>
       <c r="X3">
-        <v>0.04674225804843764</v>
+        <v>0.07448147337348829</v>
       </c>
       <c r="Y3">
-        <v>0.07408867608807299</v>
+        <v>0.0499499341850714</v>
       </c>
       <c r="Z3">
-        <v>0.4201023599658801</v>
+        <v>0.3002609630046563</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04348102418350425</v>
+        <v>0.07069414880183054</v>
       </c>
       <c r="AC3">
-        <v>-0.04348102418350425</v>
+        <v>-0.07069414880183054</v>
       </c>
       <c r="AD3">
-        <v>700</v>
+        <v>760.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>700</v>
+        <v>760.9</v>
       </c>
       <c r="AG3">
-        <v>-398</v>
+        <v>-323.3000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1545458559632623</v>
+        <v>0.1496332422174589</v>
       </c>
       <c r="AI3">
-        <v>0.2293352553811879</v>
+        <v>0.2367896931598929</v>
       </c>
       <c r="AJ3">
-        <v>-0.1159876435274232</v>
+        <v>-0.08080681846584521</v>
       </c>
       <c r="AK3">
-        <v>-0.2036534820651896</v>
+        <v>-0.1518410670674432</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Masraf Al Rayan (Q.P.S.C.) (DSM:MARK)</t>
+          <t>Qatar Islamic Bank (Q.P.S.C.) (DSM:QIBK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0344</v>
+        <v>0.0604</v>
       </c>
       <c r="E4">
-        <v>0.00992</v>
+        <v>0.108</v>
       </c>
       <c r="F4">
-        <v>0.102</v>
+        <v>0.1</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,34 +850,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.002453187141298957</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.002449876115613689</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>611.6</v>
+        <v>1065.8</v>
       </c>
       <c r="L4">
-        <v>0.5080578169131085</v>
+        <v>0.5326070661136375</v>
       </c>
       <c r="M4">
-        <v>350</v>
+        <v>427.1</v>
       </c>
       <c r="N4">
-        <v>0.02952764209123198</v>
+        <v>0.03545369271252708</v>
       </c>
       <c r="O4">
-        <v>0.5722694571615434</v>
+        <v>0.4007318446237568</v>
       </c>
       <c r="P4">
-        <v>350</v>
+        <v>427.1</v>
       </c>
       <c r="Q4">
-        <v>0.02952764209123198</v>
+        <v>0.03545369271252708</v>
       </c>
       <c r="R4">
-        <v>0.5722694571615434</v>
+        <v>0.4007318446237568</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,67 +886,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3177.9</v>
+        <v>900.9</v>
       </c>
       <c r="V4">
-        <v>0.2681025537192175</v>
+        <v>0.07478396573335436</v>
       </c>
       <c r="W4">
-        <v>0.160327155477495</v>
+        <v>0.1621457151115912</v>
       </c>
       <c r="X4">
-        <v>0.0586638983710492</v>
+        <v>0.08875458085321908</v>
       </c>
       <c r="Y4">
-        <v>0.1016632571064458</v>
+        <v>0.0733911342583721</v>
       </c>
       <c r="Z4">
-        <v>0.1221427114989865</v>
+        <v>0.1622609993026612</v>
       </c>
       <c r="AA4">
-        <v>0.0002992345115976606</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04541140516134946</v>
+        <v>0.07258189515904021</v>
       </c>
       <c r="AC4">
-        <v>-0.04511217064975179</v>
+        <v>-0.07258189515904021</v>
       </c>
       <c r="AD4">
-        <v>7934.1</v>
+        <v>8322</v>
       </c>
       <c r="AE4">
-        <v>11.08426659652158</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>7945.184266596522</v>
+        <v>8322</v>
       </c>
       <c r="AG4">
-        <v>4767.284266596522</v>
+        <v>7421.1</v>
       </c>
       <c r="AH4">
-        <v>0.4013026532541901</v>
+        <v>0.4085680480344843</v>
       </c>
       <c r="AI4">
-        <v>0.6580470784019011</v>
+        <v>0.5285856744516925</v>
       </c>
       <c r="AJ4">
-        <v>0.2868301252307746</v>
+        <v>0.3811986973361139</v>
       </c>
       <c r="AK4">
-        <v>0.5358917151525513</v>
+        <v>0.4999730512699589</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>1534.642166344294</v>
-      </c>
-      <c r="AP4">
-        <v>922.1052740031957</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qatar Islamic Bank (Q.P.S.C.) (DSM:QIBK)</t>
+          <t>Ahli Bank Q.P.S.C. (DSM:ABQK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,13 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.06309999999999999</v>
+        <v>0.0289</v>
       </c>
       <c r="E5">
-        <v>0.0944</v>
-      </c>
-      <c r="F5">
-        <v>0.117</v>
+        <v>0.0318</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -987,34 +972,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>-3.635446854751077e-05</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>-3.613848207236279e-05</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>926.7</v>
+        <v>207.6</v>
       </c>
       <c r="L5">
-        <v>0.5100445814299081</v>
+        <v>0.6940822467402206</v>
       </c>
       <c r="M5">
-        <v>315.9</v>
+        <v>118.1</v>
       </c>
       <c r="N5">
-        <v>0.02655201976902516</v>
+        <v>0.04202697412903456</v>
       </c>
       <c r="O5">
-        <v>0.3408870184525736</v>
+        <v>0.5688824662813102</v>
       </c>
       <c r="P5">
-        <v>315.9</v>
+        <v>118.1</v>
       </c>
       <c r="Q5">
-        <v>0.02655201976902516</v>
+        <v>0.04202697412903456</v>
       </c>
       <c r="R5">
-        <v>0.3408870184525736</v>
+        <v>0.5688824662813102</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1023,67 +1008,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2244.1</v>
+        <v>1209.8</v>
       </c>
       <c r="V5">
-        <v>0.1886210432531477</v>
+        <v>0.4305184868865877</v>
       </c>
       <c r="W5">
-        <v>0.1557034124703866</v>
+        <v>0.1003092385001933</v>
       </c>
       <c r="X5">
-        <v>0.05874752758125767</v>
+        <v>0.1040603538562386</v>
       </c>
       <c r="Y5">
-        <v>0.09695588488912896</v>
+        <v>-0.003751115356045359</v>
       </c>
       <c r="Z5">
-        <v>0.1667319703709105</v>
+        <v>0.06563240586324937</v>
       </c>
       <c r="AA5">
-        <v>-6.025440322138871e-06</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04709388890038098</v>
+        <v>0.0736432542566408</v>
       </c>
       <c r="AC5">
-        <v>-0.04709991434070312</v>
+        <v>-0.0736432542566408</v>
       </c>
       <c r="AD5">
-        <v>8003.6</v>
+        <v>3492.7</v>
       </c>
       <c r="AE5">
-        <v>11.83026216951986</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>8015.430262169521</v>
+        <v>3492.7</v>
       </c>
       <c r="AG5">
-        <v>5771.33026216952</v>
+        <v>2282.9</v>
       </c>
       <c r="AH5">
-        <v>0.4025259170413997</v>
+        <v>0.5541505362695945</v>
       </c>
       <c r="AI5">
-        <v>0.5422121555898309</v>
+        <v>0.6202297870829117</v>
       </c>
       <c r="AJ5">
-        <v>0.3266409174023389</v>
+        <v>0.4482426860396622</v>
       </c>
       <c r="AK5">
-        <v>0.4602802789036897</v>
+        <v>0.516317991631799</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>3479.826086956522</v>
-      </c>
-      <c r="AP5">
-        <v>2509.274027030227</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qatar National Bank (Q.P.S.C.) (DSM:QNBK)</t>
+          <t>Masraf Al Rayan (Q.P.S.C.) (DSM:MARK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,13 +1082,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00584</v>
+        <v>0.0332</v>
       </c>
       <c r="E6">
-        <v>0.00933</v>
-      </c>
-      <c r="F6">
-        <v>0.154</v>
+        <v>-0.08070000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1124,28 +1100,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3509.4</v>
+        <v>374.8</v>
       </c>
       <c r="L6">
-        <v>0.633934861540129</v>
+        <v>0.2820377756038829</v>
       </c>
       <c r="M6">
-        <v>1416.4</v>
+        <v>445</v>
       </c>
       <c r="N6">
-        <v>0.02765066920710281</v>
+        <v>0.05493420240476014</v>
       </c>
       <c r="O6">
-        <v>0.4036017552858038</v>
+        <v>1.187299893276414</v>
       </c>
       <c r="P6">
-        <v>1416.4</v>
+        <v>445</v>
       </c>
       <c r="Q6">
-        <v>0.02765066920710281</v>
+        <v>0.05493420240476014</v>
       </c>
       <c r="R6">
-        <v>0.4036017552858038</v>
+        <v>1.187299893276414</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1154,55 +1130,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>27434.3</v>
+        <v>965.7</v>
       </c>
       <c r="V6">
-        <v>0.5355667567272102</v>
+        <v>0.1192133916006222</v>
       </c>
       <c r="W6">
-        <v>0.1374935844946541</v>
+        <v>0.09198448927502087</v>
       </c>
       <c r="X6">
-        <v>0.06464429774474004</v>
+        <v>0.107080859355124</v>
       </c>
       <c r="Y6">
-        <v>0.07284928674991403</v>
+        <v>-0.01509637008010314</v>
       </c>
       <c r="Z6">
-        <v>0.1489021762811978</v>
+        <v>0.1504846673008108</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04735693592630231</v>
+        <v>0.07379383517399402</v>
       </c>
       <c r="AC6">
-        <v>-0.04735693592630231</v>
+        <v>-0.07379383517399402</v>
       </c>
       <c r="AD6">
-        <v>46862.6</v>
+        <v>10950.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>46862.6</v>
+        <v>10950.9</v>
       </c>
       <c r="AG6">
-        <v>19428.3</v>
+        <v>9985.199999999999</v>
       </c>
       <c r="AH6">
-        <v>0.4777637086924518</v>
+        <v>0.5748051334540587</v>
       </c>
       <c r="AI6">
-        <v>0.6273919161167585</v>
+        <v>0.6206058201807826</v>
       </c>
       <c r="AJ6">
-        <v>0.2749815648570267</v>
+        <v>0.5521016488073516</v>
       </c>
       <c r="AK6">
-        <v>0.4110939483707152</v>
+        <v>0.5986402714660847</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1219,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Doha Bank Q.P.S.C. (DSM:DHBK)</t>
+          <t>Qatar National Bank (Q.P.S.C.) (DSM:QNBK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1228,10 +1204,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0608</v>
+        <v>0.0306</v>
       </c>
       <c r="E7">
-        <v>-0.07719999999999999</v>
+        <v>0.0146</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1246,28 +1222,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>226.2</v>
+        <v>3827.5</v>
       </c>
       <c r="L7">
-        <v>0.4907789108266435</v>
+        <v>0.5863114841990777</v>
       </c>
       <c r="M7">
-        <v>115</v>
+        <v>1671</v>
       </c>
       <c r="N7">
-        <v>0.04219718930026052</v>
+        <v>0.03658985206400925</v>
       </c>
       <c r="O7">
-        <v>0.5083996463306808</v>
+        <v>0.4365774003919007</v>
       </c>
       <c r="P7">
-        <v>115</v>
+        <v>1671</v>
       </c>
       <c r="Q7">
-        <v>0.04219718930026052</v>
+        <v>0.03658985206400925</v>
       </c>
       <c r="R7">
-        <v>0.5083996463306808</v>
+        <v>0.4365774003919007</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1276,55 +1252,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2087.9</v>
+        <v>38302.2</v>
       </c>
       <c r="V7">
-        <v>0.7661174916522951</v>
+        <v>0.838702472606879</v>
       </c>
       <c r="W7">
-        <v>0.05983493810178817</v>
+        <v>0.1390594458694531</v>
       </c>
       <c r="X7">
-        <v>0.1080800610554606</v>
+        <v>0.1028068057925319</v>
       </c>
       <c r="Y7">
-        <v>-0.04824512295367243</v>
+        <v>0.03625264007692112</v>
       </c>
       <c r="Z7">
-        <v>0.04554797904931317</v>
+        <v>0.1390362600500506</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04797554180929688</v>
+        <v>0.07544019964643195</v>
       </c>
       <c r="AC7">
-        <v>-0.04797554180929688</v>
+        <v>-0.07544019964643195</v>
       </c>
       <c r="AD7">
-        <v>7333.8</v>
+        <v>54696.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>7333.8</v>
+        <v>54696.7</v>
       </c>
       <c r="AG7">
-        <v>5245.9</v>
+        <v>16394.5</v>
       </c>
       <c r="AH7">
-        <v>0.729071189271406</v>
+        <v>0.5449772879217974</v>
       </c>
       <c r="AI7">
-        <v>0.6487964117943682</v>
+        <v>0.6526367159534561</v>
       </c>
       <c r="AJ7">
-        <v>0.6581066840626254</v>
+        <v>0.264159425357178</v>
       </c>
       <c r="AK7">
-        <v>0.5692289329195512</v>
+        <v>0.3602664228925035</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1341,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ahli Bank Q.P.S.C. (DSM:ABQK)</t>
+          <t>Doha Bank Q.P.S.C. (DSM:DHBK)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1350,13 +1326,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0217</v>
+        <v>-0.0472</v>
       </c>
       <c r="E8">
-        <v>0.0175</v>
-      </c>
-      <c r="F8">
-        <v>0.07000000000000001</v>
+        <v>-0.0722</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1371,28 +1344,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>193.3</v>
+        <v>204.6</v>
       </c>
       <c r="L8">
-        <v>0.6721140472878998</v>
+        <v>0.4417098445595855</v>
       </c>
       <c r="M8">
-        <v>100.1</v>
+        <v>62.1</v>
       </c>
       <c r="N8">
-        <v>0.03916122217440632</v>
+        <v>0.03733541754343775</v>
       </c>
       <c r="O8">
-        <v>0.5178479048111743</v>
+        <v>0.3035190615835777</v>
       </c>
       <c r="P8">
-        <v>100.1</v>
+        <v>62.1</v>
       </c>
       <c r="Q8">
-        <v>0.03916122217440632</v>
+        <v>0.03733541754343775</v>
       </c>
       <c r="R8">
-        <v>0.5178479048111743</v>
+        <v>0.3035190615835777</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1401,55 +1374,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>725.2</v>
+        <v>1632.4</v>
       </c>
       <c r="V8">
-        <v>0.2837134697390556</v>
+        <v>0.9814224733962605</v>
       </c>
       <c r="W8">
-        <v>0.1153892072588348</v>
+        <v>0.05153782211138819</v>
       </c>
       <c r="X8">
-        <v>0.07300962287949883</v>
+        <v>0.1979641173884506</v>
       </c>
       <c r="Y8">
-        <v>0.04237958437933594</v>
+        <v>-0.1464262952770624</v>
       </c>
       <c r="Z8">
-        <v>0.06659257201074374</v>
+        <v>0.05026150741118513</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05047044572210141</v>
+        <v>0.07559879401339153</v>
       </c>
       <c r="AC8">
-        <v>-0.05047044572210141</v>
+        <v>-0.07559879401339153</v>
       </c>
       <c r="AD8">
-        <v>3212.8</v>
+        <v>7701.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>3212.8</v>
+        <v>7701.3</v>
       </c>
       <c r="AG8">
-        <v>2487.6</v>
+        <v>6068.9</v>
       </c>
       <c r="AH8">
-        <v>0.5569172632564268</v>
+        <v>0.8223842983149307</v>
       </c>
       <c r="AI8">
-        <v>0.6082083901257005</v>
+        <v>0.6639795839188875</v>
       </c>
       <c r="AJ8">
-        <v>0.4932093502785653</v>
+        <v>0.7848865782054266</v>
       </c>
       <c r="AK8">
-        <v>0.545861493899763</v>
+        <v>0.6089421349949329</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1475,10 +1448,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.09720000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="E9">
-        <v>0.306</v>
+        <v>0.556</v>
+      </c>
+      <c r="F9">
+        <v>0.176</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1493,28 +1469,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>625.9</v>
+        <v>652</v>
       </c>
       <c r="L9">
-        <v>0.6801782221256248</v>
+        <v>0.6196540581638471</v>
       </c>
       <c r="M9">
-        <v>117.8</v>
+        <v>261.6</v>
       </c>
       <c r="N9">
-        <v>0.01570017726006584</v>
+        <v>0.0470613632683901</v>
       </c>
       <c r="O9">
-        <v>0.188208979070139</v>
+        <v>0.4012269938650307</v>
       </c>
       <c r="P9">
-        <v>117.8</v>
+        <v>261.6</v>
       </c>
       <c r="Q9">
-        <v>0.01570017726006584</v>
+        <v>0.0470613632683901</v>
       </c>
       <c r="R9">
-        <v>0.188208979070139</v>
+        <v>0.4012269938650307</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1523,55 +1499,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>4412.3</v>
+        <v>4388.9</v>
       </c>
       <c r="V9">
-        <v>0.5880636003785102</v>
+        <v>0.7895551118067173</v>
       </c>
       <c r="W9">
-        <v>0.104578111946533</v>
+        <v>0.09530631038868018</v>
       </c>
       <c r="X9">
-        <v>0.08634939960543711</v>
+        <v>0.1378994122911029</v>
       </c>
       <c r="Y9">
-        <v>0.01822871234109588</v>
+        <v>-0.04259310190242274</v>
       </c>
       <c r="Z9">
-        <v>0.0587874528844311</v>
+        <v>0.06595872721346004</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05063410264620125</v>
+        <v>0.07971792152930884</v>
       </c>
       <c r="AC9">
-        <v>-0.05063410264620125</v>
+        <v>-0.07971792152930884</v>
       </c>
       <c r="AD9">
-        <v>13523.6</v>
+        <v>13694</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>13523.6</v>
+        <v>13694</v>
       </c>
       <c r="AG9">
-        <v>9111.299999999999</v>
+        <v>9305.1</v>
       </c>
       <c r="AH9">
-        <v>0.6431632162916673</v>
+        <v>0.7112768598690054</v>
       </c>
       <c r="AI9">
-        <v>0.6640706713086861</v>
+        <v>0.669980527804143</v>
       </c>
       <c r="AJ9">
-        <v>0.5483977754237287</v>
+        <v>0.6260243006499011</v>
       </c>
       <c r="AK9">
-        <v>0.5711554374263433</v>
+        <v>0.5797389489424005</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/research/traditional_assets/database/data/qatar/qatar_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0332</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="E2">
-        <v>0.0318</v>
+        <v>0.0446</v>
       </c>
       <c r="F2">
-        <v>0.138</v>
+        <v>0.107</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>6625</v>
+        <v>7170.3</v>
       </c>
       <c r="L2">
-        <v>0.5404016509780251</v>
+        <v>0.4643375210464966</v>
       </c>
       <c r="M2">
-        <v>3165.7</v>
+        <v>3415.5</v>
       </c>
       <c r="N2">
-        <v>0.03948635433817293</v>
+        <v>0.04372645966104472</v>
       </c>
       <c r="O2">
-        <v>0.4778415094339623</v>
+        <v>0.4763399020961466</v>
       </c>
       <c r="P2">
-        <v>3165.7</v>
+        <v>3415.5</v>
       </c>
       <c r="Q2">
-        <v>0.03948635433817293</v>
+        <v>0.04372645966104472</v>
       </c>
       <c r="R2">
-        <v>0.4778415094339623</v>
+        <v>0.4763399020961466</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>48484.1</v>
+        <v>41917.3</v>
       </c>
       <c r="V2">
-        <v>0.6047510352741605</v>
+        <v>0.5366403535499663</v>
       </c>
       <c r="W2">
-        <v>0.1003092385001933</v>
+        <v>0.1211640525395084</v>
       </c>
       <c r="X2">
-        <v>0.1040603538562386</v>
+        <v>0.09284780361887195</v>
       </c>
       <c r="Y2">
-        <v>-0.003751115356045359</v>
+        <v>0.02831624892063646</v>
       </c>
       <c r="Z2">
-        <v>0.1228450953749464</v>
+        <v>0.1422043609828511</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07379383517399402</v>
+        <v>0.06417693011566064</v>
       </c>
       <c r="AC2">
-        <v>-0.07379383517399402</v>
+        <v>-0.06417693011566064</v>
       </c>
       <c r="AD2">
-        <v>99618.5</v>
+        <v>107890.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>99618.5</v>
+        <v>107890.6</v>
       </c>
       <c r="AG2">
-        <v>51134.4</v>
+        <v>65973.29999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5540809998303581</v>
+        <v>0.5800532469682991</v>
       </c>
       <c r="AI2">
-        <v>0.6301737716740152</v>
+        <v>0.6417868808284115</v>
       </c>
       <c r="AJ2">
-        <v>0.3894280857597193</v>
+        <v>0.4578811373095814</v>
       </c>
       <c r="AK2">
-        <v>0.4665679412465134</v>
+        <v>0.5227993127953823</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0423</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="E3">
-        <v>0.0542</v>
+        <v>0.0581</v>
+      </c>
+      <c r="F3">
+        <v>0.108</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>292.7</v>
+        <v>315.9</v>
       </c>
       <c r="L3">
-        <v>0.4988070892978869</v>
+        <v>0.3968094460494913</v>
       </c>
       <c r="M3">
-        <v>180.8</v>
+        <v>192.7</v>
       </c>
       <c r="N3">
-        <v>0.04181120207205958</v>
+        <v>0.0433540316774658</v>
       </c>
       <c r="O3">
-        <v>0.6176973009907756</v>
+        <v>0.6100031655587211</v>
       </c>
       <c r="P3">
-        <v>180.8</v>
+        <v>192.7</v>
       </c>
       <c r="Q3">
-        <v>0.04181120207205958</v>
+        <v>0.0433540316774658</v>
       </c>
       <c r="R3">
-        <v>0.6176973009907756</v>
+        <v>0.6100031655587211</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1084.2</v>
+        <v>782.6</v>
       </c>
       <c r="V3">
-        <v>0.2507284584431803</v>
+        <v>0.1760709143268538</v>
       </c>
       <c r="W3">
-        <v>0.1244314075585597</v>
+        <v>0.1288073394495413</v>
       </c>
       <c r="X3">
-        <v>0.07448147337348829</v>
+        <v>0.06365392553944754</v>
       </c>
       <c r="Y3">
-        <v>0.0499499341850714</v>
+        <v>0.06515341391009374</v>
       </c>
       <c r="Z3">
-        <v>0.3002609630046563</v>
+        <v>0.3738962990794665</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07069414880183054</v>
+        <v>0.06115100789687056</v>
       </c>
       <c r="AC3">
-        <v>-0.07069414880183054</v>
+        <v>-0.06115100789687056</v>
       </c>
       <c r="AD3">
-        <v>760.9</v>
+        <v>755</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>760.9</v>
+        <v>755</v>
       </c>
       <c r="AG3">
-        <v>-323.3000000000001</v>
+        <v>-27.60000000000002</v>
       </c>
       <c r="AH3">
-        <v>0.1496332422174589</v>
+        <v>0.1451978922266241</v>
       </c>
       <c r="AI3">
-        <v>0.2367896931598929</v>
+        <v>0.2267267267267267</v>
       </c>
       <c r="AJ3">
-        <v>-0.08080681846584521</v>
+        <v>-0.00624830209182288</v>
       </c>
       <c r="AK3">
-        <v>-0.1518410670674432</v>
+        <v>-0.0108345764308707</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,14 +838,14 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0604</v>
+        <v>0.103</v>
       </c>
       <c r="E4">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="F4">
         <v>0.108</v>
       </c>
-      <c r="F4">
-        <v>0.1</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -856,28 +859,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1065.8</v>
+        <v>1156.5</v>
       </c>
       <c r="L4">
-        <v>0.5326070661136375</v>
+        <v>0.4389160878970739</v>
       </c>
       <c r="M4">
-        <v>427.1</v>
+        <v>459.7</v>
       </c>
       <c r="N4">
-        <v>0.03545369271252708</v>
+        <v>0.0329415979935507</v>
       </c>
       <c r="O4">
-        <v>0.4007318446237568</v>
+        <v>0.3974924340683095</v>
       </c>
       <c r="P4">
-        <v>427.1</v>
+        <v>459.7</v>
       </c>
       <c r="Q4">
-        <v>0.03545369271252708</v>
+        <v>0.0329415979935507</v>
       </c>
       <c r="R4">
-        <v>0.4007318446237568</v>
+        <v>0.3974924340683095</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>900.9</v>
+        <v>1095.6</v>
       </c>
       <c r="V4">
-        <v>0.07478396573335436</v>
+        <v>0.07850949480472948</v>
       </c>
       <c r="W4">
-        <v>0.1621457151115912</v>
+        <v>0.1598457519591989</v>
       </c>
       <c r="X4">
-        <v>0.08875458085321908</v>
+        <v>0.07277476347785533</v>
       </c>
       <c r="Y4">
-        <v>0.0733911342583721</v>
+        <v>0.08707098848134356</v>
       </c>
       <c r="Z4">
-        <v>0.1622609993026612</v>
+        <v>0.1797805706799853</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07258189515904021</v>
+        <v>0.06248888904490548</v>
       </c>
       <c r="AC4">
-        <v>-0.07258189515904021</v>
+        <v>-0.06248888904490548</v>
       </c>
       <c r="AD4">
-        <v>8322</v>
+        <v>8930.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>8322</v>
+        <v>8930.5</v>
       </c>
       <c r="AG4">
-        <v>7421.1</v>
+        <v>7834.9</v>
       </c>
       <c r="AH4">
-        <v>0.4085680480344843</v>
+        <v>0.3902252517969894</v>
       </c>
       <c r="AI4">
-        <v>0.5285856744516925</v>
+        <v>0.5263514628568734</v>
       </c>
       <c r="AJ4">
-        <v>0.3811986973361139</v>
+        <v>0.3595656703335031</v>
       </c>
       <c r="AK4">
-        <v>0.4999730512699589</v>
+        <v>0.4936551741519229</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ahli Bank Q.P.S.C. (DSM:ABQK)</t>
+          <t>Masraf Al Rayan (Q.P.S.C.) (DSM:MARK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0289</v>
+        <v>0.105</v>
       </c>
       <c r="E5">
-        <v>0.0318</v>
+        <v>-0.0983</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,28 +981,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>207.6</v>
+        <v>343.6</v>
       </c>
       <c r="L5">
-        <v>0.6940822467402206</v>
+        <v>0.1613145539906103</v>
       </c>
       <c r="M5">
-        <v>118.1</v>
+        <v>319.4</v>
       </c>
       <c r="N5">
-        <v>0.04202697412903456</v>
+        <v>0.04709178031699226</v>
       </c>
       <c r="O5">
-        <v>0.5688824662813102</v>
+        <v>0.9295692665890569</v>
       </c>
       <c r="P5">
-        <v>118.1</v>
+        <v>319.4</v>
       </c>
       <c r="Q5">
-        <v>0.04202697412903456</v>
+        <v>0.04709178031699226</v>
       </c>
       <c r="R5">
-        <v>0.5688824662813102</v>
+        <v>0.9295692665890569</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +1011,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1209.8</v>
+        <v>1762.8</v>
       </c>
       <c r="V5">
-        <v>0.4305184868865877</v>
+        <v>0.2599041651308515</v>
       </c>
       <c r="W5">
-        <v>0.1003092385001933</v>
+        <v>0.05169638155420146</v>
       </c>
       <c r="X5">
-        <v>0.1040603538562386</v>
+        <v>0.09284780361887195</v>
       </c>
       <c r="Y5">
-        <v>-0.003751115356045359</v>
+        <v>-0.04115142206467048</v>
       </c>
       <c r="Z5">
-        <v>0.06563240586324937</v>
+        <v>0.1318999789455433</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0736432542566408</v>
+        <v>0.06377679833997063</v>
       </c>
       <c r="AC5">
-        <v>-0.0736432542566408</v>
+        <v>-0.06377679833997063</v>
       </c>
       <c r="AD5">
-        <v>3492.7</v>
+        <v>11357.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3492.7</v>
+        <v>11357.4</v>
       </c>
       <c r="AG5">
-        <v>2282.9</v>
+        <v>9594.6</v>
       </c>
       <c r="AH5">
-        <v>0.5541505362695945</v>
+        <v>0.6261004746442923</v>
       </c>
       <c r="AI5">
-        <v>0.6202297870829117</v>
+        <v>0.6268918695148203</v>
       </c>
       <c r="AJ5">
-        <v>0.4482426860396622</v>
+        <v>0.5858546384891098</v>
       </c>
       <c r="AK5">
-        <v>0.516317991631799</v>
+        <v>0.5866749825732839</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Masraf Al Rayan (Q.P.S.C.) (DSM:MARK)</t>
+          <t>Ahli Bank Q.P.S.C. (DSM:ABQK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,10 +1085,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0332</v>
+        <v>0.0358</v>
       </c>
       <c r="E6">
-        <v>-0.08070000000000001</v>
+        <v>0.0446</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,28 +1103,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>374.8</v>
+        <v>225.3</v>
       </c>
       <c r="L6">
-        <v>0.2820377756038829</v>
+        <v>0.6983880967141971</v>
       </c>
       <c r="M6">
-        <v>445</v>
+        <v>152.2</v>
       </c>
       <c r="N6">
-        <v>0.05493420240476014</v>
+        <v>0.05996375384130486</v>
       </c>
       <c r="O6">
-        <v>1.187299893276414</v>
+        <v>0.6755437194851308</v>
       </c>
       <c r="P6">
-        <v>445</v>
+        <v>152.2</v>
       </c>
       <c r="Q6">
-        <v>0.05493420240476014</v>
+        <v>0.05996375384130486</v>
       </c>
       <c r="R6">
-        <v>1.187299893276414</v>
+        <v>0.6755437194851308</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>965.7</v>
+        <v>2902.8</v>
       </c>
       <c r="V6">
-        <v>0.1192133916006222</v>
+        <v>1.143645102828776</v>
       </c>
       <c r="W6">
-        <v>0.09198448927502087</v>
+        <v>0.1053492939306088</v>
       </c>
       <c r="X6">
-        <v>0.107080859355124</v>
+        <v>0.1054976931574213</v>
       </c>
       <c r="Y6">
-        <v>-0.01509637008010314</v>
+        <v>-0.0001483992268125067</v>
       </c>
       <c r="Z6">
-        <v>0.1504846673008108</v>
+        <v>0.07296166459346377</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07379383517399402</v>
+        <v>0.06417693011566064</v>
       </c>
       <c r="AC6">
-        <v>-0.07379383517399402</v>
+        <v>-0.06417693011566064</v>
       </c>
       <c r="AD6">
-        <v>10950.9</v>
+        <v>5905.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>10950.9</v>
+        <v>5905.1</v>
       </c>
       <c r="AG6">
-        <v>9985.199999999999</v>
+        <v>3002.3</v>
       </c>
       <c r="AH6">
-        <v>0.5748051334540587</v>
+        <v>0.6993829426882855</v>
       </c>
       <c r="AI6">
-        <v>0.6206058201807826</v>
+        <v>0.7279013867488444</v>
       </c>
       <c r="AJ6">
-        <v>0.5521016488073516</v>
+        <v>0.5418825015792799</v>
       </c>
       <c r="AK6">
-        <v>0.5986402714660847</v>
+        <v>0.5762903814039195</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qatar National Bank (Q.P.S.C.) (DSM:QNBK)</t>
+          <t>Doha Bank Q.P.S.C. (DSM:DHBK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,10 +1207,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0306</v>
+        <v>-0.0373</v>
       </c>
       <c r="E7">
-        <v>0.0146</v>
+        <v>-0.105</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,28 +1225,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3827.5</v>
+        <v>126.2</v>
       </c>
       <c r="L7">
-        <v>0.5863114841990777</v>
+        <v>0.3079551000488043</v>
       </c>
       <c r="M7">
-        <v>1671</v>
+        <v>116.1</v>
       </c>
       <c r="N7">
-        <v>0.03658985206400925</v>
+        <v>0.07449470644850818</v>
       </c>
       <c r="O7">
-        <v>0.4365774003919007</v>
+        <v>0.9199683042789223</v>
       </c>
       <c r="P7">
-        <v>1671</v>
+        <v>116.1</v>
       </c>
       <c r="Q7">
-        <v>0.03658985206400925</v>
+        <v>0.07449470644850818</v>
       </c>
       <c r="R7">
-        <v>0.4365774003919007</v>
+        <v>0.9199683042789223</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1252,55 +1255,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>38302.2</v>
+        <v>1283.3</v>
       </c>
       <c r="V7">
-        <v>0.838702472606879</v>
+        <v>0.8234199550850176</v>
       </c>
       <c r="W7">
-        <v>0.1390594458694531</v>
+        <v>0.03238056139990763</v>
       </c>
       <c r="X7">
-        <v>0.1028068057925319</v>
+        <v>0.1741531814598082</v>
       </c>
       <c r="Y7">
-        <v>0.03625264007692112</v>
+        <v>-0.1417726200599005</v>
       </c>
       <c r="Z7">
-        <v>0.1390362600500506</v>
+        <v>0.04111856957948285</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07544019964643195</v>
+        <v>0.06502298047574231</v>
       </c>
       <c r="AC7">
-        <v>-0.07544019964643195</v>
+        <v>-0.06502298047574231</v>
       </c>
       <c r="AD7">
-        <v>54696.7</v>
+        <v>9140.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>54696.7</v>
+        <v>9140.6</v>
       </c>
       <c r="AG7">
-        <v>16394.5</v>
+        <v>7857.3</v>
       </c>
       <c r="AH7">
-        <v>0.5449772879217974</v>
+        <v>0.8543335420736323</v>
       </c>
       <c r="AI7">
-        <v>0.6526367159534561</v>
+        <v>0.6983421193368478</v>
       </c>
       <c r="AJ7">
-        <v>0.264159425357178</v>
+        <v>0.834480341553559</v>
       </c>
       <c r="AK7">
-        <v>0.3602664228925035</v>
+        <v>0.6655513861948041</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1317,7 +1320,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Doha Bank Q.P.S.C. (DSM:DHBK)</t>
+          <t>Qatar National Bank (Q.P.S.C.) (DSM:QNBK)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,10 +1329,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.0472</v>
+        <v>0.0653</v>
       </c>
       <c r="E8">
-        <v>-0.0722</v>
+        <v>0.0215</v>
+      </c>
+      <c r="F8">
+        <v>0.098</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1344,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>204.6</v>
+        <v>4185.5</v>
       </c>
       <c r="L8">
-        <v>0.4417098445595855</v>
+        <v>0.5285256086473381</v>
       </c>
       <c r="M8">
-        <v>62.1</v>
+        <v>1819.5</v>
       </c>
       <c r="N8">
-        <v>0.03733541754343775</v>
+        <v>0.04338454275147893</v>
       </c>
       <c r="O8">
-        <v>0.3035190615835777</v>
+        <v>0.4347150878031298</v>
       </c>
       <c r="P8">
-        <v>62.1</v>
+        <v>1819.5</v>
       </c>
       <c r="Q8">
-        <v>0.03733541754343775</v>
+        <v>0.04338454275147893</v>
       </c>
       <c r="R8">
-        <v>0.3035190615835777</v>
+        <v>0.4347150878031298</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1374,55 +1380,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1632.4</v>
+        <v>28841.5</v>
       </c>
       <c r="V8">
-        <v>0.9814224733962605</v>
+        <v>0.6877028248237317</v>
       </c>
       <c r="W8">
-        <v>0.05153782211138819</v>
+        <v>0.1452118764614861</v>
       </c>
       <c r="X8">
-        <v>0.1979641173884506</v>
+        <v>0.08717029142224197</v>
       </c>
       <c r="Y8">
-        <v>-0.1464262952770624</v>
+        <v>0.05804158503924417</v>
       </c>
       <c r="Z8">
-        <v>0.05026150741118513</v>
+        <v>0.1751341835865885</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07559879401339153</v>
+        <v>0.06508460934037902</v>
       </c>
       <c r="AC8">
-        <v>-0.07559879401339153</v>
+        <v>-0.06508460934037902</v>
       </c>
       <c r="AD8">
-        <v>7701.3</v>
+        <v>57955.2</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>7701.3</v>
+        <v>57955.2</v>
       </c>
       <c r="AG8">
-        <v>6068.9</v>
+        <v>29113.7</v>
       </c>
       <c r="AH8">
-        <v>0.8223842983149307</v>
+        <v>0.5801663962135901</v>
       </c>
       <c r="AI8">
-        <v>0.6639795839188875</v>
+        <v>0.6603535166509237</v>
       </c>
       <c r="AJ8">
-        <v>0.7848865782054266</v>
+        <v>0.4097485524808381</v>
       </c>
       <c r="AK8">
-        <v>0.6089421349949329</v>
+        <v>0.494102412664793</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1448,13 +1454,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.156</v>
+        <v>0.11</v>
       </c>
       <c r="E9">
-        <v>0.556</v>
+        <v>0.131</v>
       </c>
       <c r="F9">
-        <v>0.176</v>
+        <v>0.106</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1469,28 +1475,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>652</v>
+        <v>817.3</v>
       </c>
       <c r="L9">
-        <v>0.6196540581638471</v>
+        <v>0.6647958353668455</v>
       </c>
       <c r="M9">
-        <v>261.6</v>
+        <v>355.9</v>
       </c>
       <c r="N9">
-        <v>0.0470613632683901</v>
+        <v>0.05163433777764882</v>
       </c>
       <c r="O9">
-        <v>0.4012269938650307</v>
+        <v>0.4354582160773278</v>
       </c>
       <c r="P9">
-        <v>261.6</v>
+        <v>355.9</v>
       </c>
       <c r="Q9">
-        <v>0.0470613632683901</v>
+        <v>0.05163433777764882</v>
       </c>
       <c r="R9">
-        <v>0.4012269938650307</v>
+        <v>0.4354582160773278</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1499,55 +1505,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>4388.9</v>
+        <v>5248.7</v>
       </c>
       <c r="V9">
-        <v>0.7895551118067173</v>
+        <v>0.761486790372423</v>
       </c>
       <c r="W9">
-        <v>0.09530631038868018</v>
+        <v>0.1211640525395084</v>
       </c>
       <c r="X9">
-        <v>0.1378994122911029</v>
+        <v>0.09933582001694821</v>
       </c>
       <c r="Y9">
-        <v>-0.04259310190242274</v>
+        <v>0.02182823252256019</v>
       </c>
       <c r="Z9">
-        <v>0.06595872721346004</v>
+        <v>0.07659574468085106</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07971792152930884</v>
+        <v>0.06749604529509237</v>
       </c>
       <c r="AC9">
-        <v>-0.07971792152930884</v>
+        <v>-0.06749604529509237</v>
       </c>
       <c r="AD9">
-        <v>13694</v>
+        <v>13846.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>13694</v>
+        <v>13846.8</v>
       </c>
       <c r="AG9">
-        <v>9305.1</v>
+        <v>8598.099999999999</v>
       </c>
       <c r="AH9">
-        <v>0.7112768598690054</v>
+        <v>0.667653511415415</v>
       </c>
       <c r="AI9">
-        <v>0.669980527804143</v>
+        <v>0.6679433684667518</v>
       </c>
       <c r="AJ9">
-        <v>0.6260243006499011</v>
+        <v>0.5550455754383247</v>
       </c>
       <c r="AK9">
-        <v>0.5797389489424005</v>
+        <v>0.5553682388352775</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/research/traditional_assets/database/data/qatar/qatar_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08289999999999999</v>
+        <v>0.08115</v>
       </c>
       <c r="E2">
-        <v>0.0446</v>
+        <v>0.06544999999999999</v>
       </c>
       <c r="F2">
-        <v>0.107</v>
+        <v>0.0999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>7170.3</v>
+        <v>5335.4</v>
       </c>
       <c r="L2">
-        <v>0.4643375210464966</v>
+        <v>0.5459382578354429</v>
       </c>
       <c r="M2">
-        <v>3415.5</v>
+        <v>3159.9</v>
       </c>
       <c r="N2">
-        <v>0.04372645966104472</v>
+        <v>0.06488088027250832</v>
       </c>
       <c r="O2">
-        <v>0.4763399020961466</v>
+        <v>0.5922517524459273</v>
       </c>
       <c r="P2">
-        <v>3415.5</v>
+        <v>3159.9</v>
       </c>
       <c r="Q2">
-        <v>0.04372645966104472</v>
+        <v>0.06488088027250832</v>
       </c>
       <c r="R2">
-        <v>0.4763399020961466</v>
+        <v>0.5922517524459273</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>41917.3</v>
+        <v>29873.2</v>
       </c>
       <c r="V2">
-        <v>0.5366403535499663</v>
+        <v>0.6133736866852418</v>
       </c>
       <c r="W2">
-        <v>0.1211640525395084</v>
+        <v>0.1374198544783234</v>
       </c>
       <c r="X2">
-        <v>0.09284780361887195</v>
+        <v>0.102520087691065</v>
       </c>
       <c r="Y2">
-        <v>0.02831624892063646</v>
+        <v>0.03489976678725837</v>
       </c>
       <c r="Z2">
-        <v>0.1422043609828511</v>
+        <v>0.1318700150181959</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06417693011566064</v>
+        <v>0.06918943762740948</v>
       </c>
       <c r="AC2">
-        <v>-0.06417693011566064</v>
+        <v>-0.06918943762740948</v>
       </c>
       <c r="AD2">
-        <v>107890.6</v>
+        <v>72440.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>107890.6</v>
+        <v>72440.2</v>
       </c>
       <c r="AG2">
-        <v>65973.29999999999</v>
+        <v>42567</v>
       </c>
       <c r="AH2">
-        <v>0.5800532469682991</v>
+        <v>0.5979711630771162</v>
       </c>
       <c r="AI2">
-        <v>0.6417868808284115</v>
+        <v>0.6545775573770343</v>
       </c>
       <c r="AJ2">
-        <v>0.4578811373095814</v>
+        <v>0.4663849387696518</v>
       </c>
       <c r="AK2">
-        <v>0.5227993127953823</v>
+        <v>0.5268590821831847</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qatar International Islamic Bank (Q.P.S.C) (DSM:QIIK)</t>
+          <t>Qatar National Bank (Q.P.S.C.) (DSM:QNBK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08289999999999999</v>
+        <v>0.0757</v>
       </c>
       <c r="E3">
-        <v>0.0581</v>
+        <v>0.0289</v>
       </c>
       <c r="F3">
-        <v>0.108</v>
+        <v>0.0999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>315.9</v>
+        <v>4490.9</v>
       </c>
       <c r="L3">
-        <v>0.3968094460494913</v>
+        <v>0.5234454222274025</v>
       </c>
       <c r="M3">
-        <v>192.7</v>
+        <v>2804</v>
       </c>
       <c r="N3">
-        <v>0.0433540316774658</v>
+        <v>0.06392034121243484</v>
       </c>
       <c r="O3">
-        <v>0.6100031655587211</v>
+        <v>0.624373733550068</v>
       </c>
       <c r="P3">
-        <v>192.7</v>
+        <v>2804</v>
       </c>
       <c r="Q3">
-        <v>0.0433540316774658</v>
+        <v>0.06392034121243484</v>
       </c>
       <c r="R3">
-        <v>0.6100031655587211</v>
+        <v>0.624373733550068</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>782.6</v>
+        <v>25959.8</v>
       </c>
       <c r="V3">
-        <v>0.1760709143268538</v>
+        <v>0.5917829079196026</v>
       </c>
       <c r="W3">
-        <v>0.1288073394495413</v>
+        <v>0.152158592696496</v>
       </c>
       <c r="X3">
-        <v>0.06365392553944754</v>
+        <v>0.08908300212760197</v>
       </c>
       <c r="Y3">
-        <v>0.06515341391009374</v>
+        <v>0.06307559056889399</v>
       </c>
       <c r="Z3">
-        <v>0.3738962990794665</v>
+        <v>0.1463371784615962</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06115100789687056</v>
+        <v>0.06818593062433446</v>
       </c>
       <c r="AC3">
-        <v>-0.06115100789687056</v>
+        <v>-0.06818593062433446</v>
       </c>
       <c r="AD3">
-        <v>755</v>
+        <v>58627.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>755</v>
+        <v>58627.7</v>
       </c>
       <c r="AG3">
-        <v>-27.60000000000002</v>
+        <v>32667.9</v>
       </c>
       <c r="AH3">
-        <v>0.1451978922266241</v>
+        <v>0.572006579846002</v>
       </c>
       <c r="AI3">
-        <v>0.2267267267267267</v>
+        <v>0.6542503389669737</v>
       </c>
       <c r="AJ3">
-        <v>-0.00624830209182288</v>
+        <v>0.4268360880642843</v>
       </c>
       <c r="AK3">
-        <v>-0.0108345764308707</v>
+        <v>0.5132370893014531</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qatar Islamic Bank (Q.P.S.C.) (DSM:QIBK)</t>
+          <t>The Commercial Bank (P.S.Q.C.) (DSM:CBQK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.103</v>
+        <v>0.0866</v>
       </c>
       <c r="E4">
-        <v>0.09820000000000001</v>
-      </c>
-      <c r="F4">
-        <v>0.108</v>
+        <v>0.102</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1156.5</v>
+        <v>844.5</v>
       </c>
       <c r="L4">
-        <v>0.4389160878970739</v>
+        <v>0.7076420311714429</v>
       </c>
       <c r="M4">
-        <v>459.7</v>
+        <v>355.9</v>
       </c>
       <c r="N4">
-        <v>0.0329415979935507</v>
+        <v>0.07359387923904052</v>
       </c>
       <c r="O4">
-        <v>0.3974924340683095</v>
+        <v>0.421432800473653</v>
       </c>
       <c r="P4">
-        <v>459.7</v>
+        <v>355.9</v>
       </c>
       <c r="Q4">
-        <v>0.0329415979935507</v>
+        <v>0.07359387923904052</v>
       </c>
       <c r="R4">
-        <v>0.3974924340683095</v>
+        <v>0.421432800473653</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,676 +886,60 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1095.6</v>
+        <v>3913.4</v>
       </c>
       <c r="V4">
-        <v>0.07850949480472948</v>
+        <v>0.8092224979321754</v>
       </c>
       <c r="W4">
-        <v>0.1598457519591989</v>
+        <v>0.1226811162601508</v>
       </c>
       <c r="X4">
-        <v>0.07277476347785533</v>
+        <v>0.1159571732545281</v>
       </c>
       <c r="Y4">
-        <v>0.08707098848134356</v>
+        <v>0.006723943005622735</v>
       </c>
       <c r="Z4">
-        <v>0.1797805706799853</v>
+        <v>0.07708405999302408</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06248888904490548</v>
+        <v>0.07019294463048451</v>
       </c>
       <c r="AC4">
-        <v>-0.06248888904490548</v>
+        <v>-0.07019294463048451</v>
       </c>
       <c r="AD4">
-        <v>8930.5</v>
+        <v>13812.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>8930.5</v>
+        <v>13812.5</v>
       </c>
       <c r="AG4">
-        <v>7834.9</v>
+        <v>9899.1</v>
       </c>
       <c r="AH4">
-        <v>0.3902252517969894</v>
+        <v>0.7406761937957477</v>
       </c>
       <c r="AI4">
-        <v>0.5263514628568734</v>
+        <v>0.6559700996362187</v>
       </c>
       <c r="AJ4">
-        <v>0.3595656703335031</v>
+        <v>0.6718040596941995</v>
       </c>
       <c r="AK4">
-        <v>0.4936551741519229</v>
+        <v>0.5774359512809744</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Masraf Al Rayan (Q.P.S.C.) (DSM:MARK)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.105</v>
-      </c>
-      <c r="E5">
-        <v>-0.0983</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>343.6</v>
-      </c>
-      <c r="L5">
-        <v>0.1613145539906103</v>
-      </c>
-      <c r="M5">
-        <v>319.4</v>
-      </c>
-      <c r="N5">
-        <v>0.04709178031699226</v>
-      </c>
-      <c r="O5">
-        <v>0.9295692665890569</v>
-      </c>
-      <c r="P5">
-        <v>319.4</v>
-      </c>
-      <c r="Q5">
-        <v>0.04709178031699226</v>
-      </c>
-      <c r="R5">
-        <v>0.9295692665890569</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>1762.8</v>
-      </c>
-      <c r="V5">
-        <v>0.2599041651308515</v>
-      </c>
-      <c r="W5">
-        <v>0.05169638155420146</v>
-      </c>
-      <c r="X5">
-        <v>0.09284780361887195</v>
-      </c>
-      <c r="Y5">
-        <v>-0.04115142206467048</v>
-      </c>
-      <c r="Z5">
-        <v>0.1318999789455433</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06377679833997063</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06377679833997063</v>
-      </c>
-      <c r="AD5">
-        <v>11357.4</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>11357.4</v>
-      </c>
-      <c r="AG5">
-        <v>9594.6</v>
-      </c>
-      <c r="AH5">
-        <v>0.6261004746442923</v>
-      </c>
-      <c r="AI5">
-        <v>0.6268918695148203</v>
-      </c>
-      <c r="AJ5">
-        <v>0.5858546384891098</v>
-      </c>
-      <c r="AK5">
-        <v>0.5866749825732839</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ahli Bank Q.P.S.C. (DSM:ABQK)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0358</v>
-      </c>
-      <c r="E6">
-        <v>0.0446</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>225.3</v>
-      </c>
-      <c r="L6">
-        <v>0.6983880967141971</v>
-      </c>
-      <c r="M6">
-        <v>152.2</v>
-      </c>
-      <c r="N6">
-        <v>0.05996375384130486</v>
-      </c>
-      <c r="O6">
-        <v>0.6755437194851308</v>
-      </c>
-      <c r="P6">
-        <v>152.2</v>
-      </c>
-      <c r="Q6">
-        <v>0.05996375384130486</v>
-      </c>
-      <c r="R6">
-        <v>0.6755437194851308</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>2902.8</v>
-      </c>
-      <c r="V6">
-        <v>1.143645102828776</v>
-      </c>
-      <c r="W6">
-        <v>0.1053492939306088</v>
-      </c>
-      <c r="X6">
-        <v>0.1054976931574213</v>
-      </c>
-      <c r="Y6">
-        <v>-0.0001483992268125067</v>
-      </c>
-      <c r="Z6">
-        <v>0.07296166459346377</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.06417693011566064</v>
-      </c>
-      <c r="AC6">
-        <v>-0.06417693011566064</v>
-      </c>
-      <c r="AD6">
-        <v>5905.1</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>5905.1</v>
-      </c>
-      <c r="AG6">
-        <v>3002.3</v>
-      </c>
-      <c r="AH6">
-        <v>0.6993829426882855</v>
-      </c>
-      <c r="AI6">
-        <v>0.7279013867488444</v>
-      </c>
-      <c r="AJ6">
-        <v>0.5418825015792799</v>
-      </c>
-      <c r="AK6">
-        <v>0.5762903814039195</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Doha Bank Q.P.S.C. (DSM:DHBK)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>-0.0373</v>
-      </c>
-      <c r="E7">
-        <v>-0.105</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>126.2</v>
-      </c>
-      <c r="L7">
-        <v>0.3079551000488043</v>
-      </c>
-      <c r="M7">
-        <v>116.1</v>
-      </c>
-      <c r="N7">
-        <v>0.07449470644850818</v>
-      </c>
-      <c r="O7">
-        <v>0.9199683042789223</v>
-      </c>
-      <c r="P7">
-        <v>116.1</v>
-      </c>
-      <c r="Q7">
-        <v>0.07449470644850818</v>
-      </c>
-      <c r="R7">
-        <v>0.9199683042789223</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>1283.3</v>
-      </c>
-      <c r="V7">
-        <v>0.8234199550850176</v>
-      </c>
-      <c r="W7">
-        <v>0.03238056139990763</v>
-      </c>
-      <c r="X7">
-        <v>0.1741531814598082</v>
-      </c>
-      <c r="Y7">
-        <v>-0.1417726200599005</v>
-      </c>
-      <c r="Z7">
-        <v>0.04111856957948285</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.06502298047574231</v>
-      </c>
-      <c r="AC7">
-        <v>-0.06502298047574231</v>
-      </c>
-      <c r="AD7">
-        <v>9140.6</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>9140.6</v>
-      </c>
-      <c r="AG7">
-        <v>7857.3</v>
-      </c>
-      <c r="AH7">
-        <v>0.8543335420736323</v>
-      </c>
-      <c r="AI7">
-        <v>0.6983421193368478</v>
-      </c>
-      <c r="AJ7">
-        <v>0.834480341553559</v>
-      </c>
-      <c r="AK7">
-        <v>0.6655513861948041</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Qatar National Bank (Q.P.S.C.) (DSM:QNBK)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0653</v>
-      </c>
-      <c r="E8">
-        <v>0.0215</v>
-      </c>
-      <c r="F8">
-        <v>0.098</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>4185.5</v>
-      </c>
-      <c r="L8">
-        <v>0.5285256086473381</v>
-      </c>
-      <c r="M8">
-        <v>1819.5</v>
-      </c>
-      <c r="N8">
-        <v>0.04338454275147893</v>
-      </c>
-      <c r="O8">
-        <v>0.4347150878031298</v>
-      </c>
-      <c r="P8">
-        <v>1819.5</v>
-      </c>
-      <c r="Q8">
-        <v>0.04338454275147893</v>
-      </c>
-      <c r="R8">
-        <v>0.4347150878031298</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>28841.5</v>
-      </c>
-      <c r="V8">
-        <v>0.6877028248237317</v>
-      </c>
-      <c r="W8">
-        <v>0.1452118764614861</v>
-      </c>
-      <c r="X8">
-        <v>0.08717029142224197</v>
-      </c>
-      <c r="Y8">
-        <v>0.05804158503924417</v>
-      </c>
-      <c r="Z8">
-        <v>0.1751341835865885</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.06508460934037902</v>
-      </c>
-      <c r="AC8">
-        <v>-0.06508460934037902</v>
-      </c>
-      <c r="AD8">
-        <v>57955.2</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>57955.2</v>
-      </c>
-      <c r="AG8">
-        <v>29113.7</v>
-      </c>
-      <c r="AH8">
-        <v>0.5801663962135901</v>
-      </c>
-      <c r="AI8">
-        <v>0.6603535166509237</v>
-      </c>
-      <c r="AJ8">
-        <v>0.4097485524808381</v>
-      </c>
-      <c r="AK8">
-        <v>0.494102412664793</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>The Commercial Bank (P.S.Q.C.) (DSM:CBQK)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.11</v>
-      </c>
-      <c r="E9">
-        <v>0.131</v>
-      </c>
-      <c r="F9">
-        <v>0.106</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>817.3</v>
-      </c>
-      <c r="L9">
-        <v>0.6647958353668455</v>
-      </c>
-      <c r="M9">
-        <v>355.9</v>
-      </c>
-      <c r="N9">
-        <v>0.05163433777764882</v>
-      </c>
-      <c r="O9">
-        <v>0.4354582160773278</v>
-      </c>
-      <c r="P9">
-        <v>355.9</v>
-      </c>
-      <c r="Q9">
-        <v>0.05163433777764882</v>
-      </c>
-      <c r="R9">
-        <v>0.4354582160773278</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>5248.7</v>
-      </c>
-      <c r="V9">
-        <v>0.761486790372423</v>
-      </c>
-      <c r="W9">
-        <v>0.1211640525395084</v>
-      </c>
-      <c r="X9">
-        <v>0.09933582001694821</v>
-      </c>
-      <c r="Y9">
-        <v>0.02182823252256019</v>
-      </c>
-      <c r="Z9">
-        <v>0.07659574468085106</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.06749604529509237</v>
-      </c>
-      <c r="AC9">
-        <v>-0.06749604529509237</v>
-      </c>
-      <c r="AD9">
-        <v>13846.8</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>13846.8</v>
-      </c>
-      <c r="AG9">
-        <v>8598.099999999999</v>
-      </c>
-      <c r="AH9">
-        <v>0.667653511415415</v>
-      </c>
-      <c r="AI9">
-        <v>0.6679433684667518</v>
-      </c>
-      <c r="AJ9">
-        <v>0.5550455754383247</v>
-      </c>
-      <c r="AK9">
-        <v>0.5553682388352775</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/qatar/qatar_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08115</v>
+        <v>0.0866</v>
       </c>
       <c r="E2">
-        <v>0.06544999999999999</v>
+        <v>0.0525</v>
       </c>
       <c r="F2">
-        <v>0.0999</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>5335.4</v>
+        <v>7793</v>
       </c>
       <c r="L2">
-        <v>0.5459382578354429</v>
+        <v>0.4544818335568904</v>
       </c>
       <c r="M2">
-        <v>3159.9</v>
+        <v>4770.7</v>
       </c>
       <c r="N2">
-        <v>0.06488088027250832</v>
+        <v>0.06155368642159766</v>
       </c>
       <c r="O2">
-        <v>0.5922517524459273</v>
+        <v>0.6121775952778133</v>
       </c>
       <c r="P2">
-        <v>3159.9</v>
+        <v>4770.7</v>
       </c>
       <c r="Q2">
-        <v>0.06488088027250832</v>
+        <v>0.06155368642159766</v>
       </c>
       <c r="R2">
-        <v>0.5922517524459273</v>
+        <v>0.6121775952778133</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>29873.2</v>
+        <v>36128.1</v>
       </c>
       <c r="V2">
-        <v>0.6133736866852418</v>
+        <v>0.4661407630763038</v>
       </c>
       <c r="W2">
-        <v>0.1374198544783234</v>
+        <v>0.1226811162601508</v>
       </c>
       <c r="X2">
-        <v>0.102520087691065</v>
+        <v>0.08630287004781978</v>
       </c>
       <c r="Y2">
-        <v>0.03489976678725837</v>
+        <v>0.03637824621233102</v>
       </c>
       <c r="Z2">
-        <v>0.1318700150181959</v>
+        <v>0.1408985394112451</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06918943762740948</v>
+        <v>0.06720184989212233</v>
       </c>
       <c r="AC2">
-        <v>-0.06918943762740948</v>
+        <v>-0.06720184989212233</v>
       </c>
       <c r="AD2">
-        <v>72440.2</v>
+        <v>103306.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>72440.2</v>
+        <v>103306.7</v>
       </c>
       <c r="AG2">
-        <v>42567</v>
+        <v>67178.60000000001</v>
       </c>
       <c r="AH2">
-        <v>0.5979711630771162</v>
+        <v>0.5713505896199023</v>
       </c>
       <c r="AI2">
-        <v>0.6545775573770343</v>
+        <v>0.6226040639607345</v>
       </c>
       <c r="AJ2">
-        <v>0.4663849387696518</v>
+        <v>0.4643148172594903</v>
       </c>
       <c r="AK2">
-        <v>0.5268590821831847</v>
+        <v>0.5175598831113101</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qatar National Bank (Q.P.S.C.) (DSM:QNBK)</t>
+          <t>Qatar International Islamic Bank (Q.P.S.C) (DSM:QIIK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0757</v>
+        <v>0.09970000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0289</v>
-      </c>
-      <c r="F3">
-        <v>0.0999</v>
+        <v>0.05860000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +731,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4490.9</v>
+        <v>337.4</v>
       </c>
       <c r="L3">
-        <v>0.5234454222274025</v>
+        <v>0.3469408740359897</v>
       </c>
       <c r="M3">
-        <v>2804</v>
+        <v>312.7</v>
       </c>
       <c r="N3">
-        <v>0.06392034121243484</v>
+        <v>0.06899671234085743</v>
       </c>
       <c r="O3">
-        <v>0.624373733550068</v>
+        <v>0.9267931238885596</v>
       </c>
       <c r="P3">
-        <v>2804</v>
+        <v>312.7</v>
       </c>
       <c r="Q3">
-        <v>0.06392034121243484</v>
+        <v>0.06899671234085743</v>
       </c>
       <c r="R3">
-        <v>0.624373733550068</v>
+        <v>0.9267931238885596</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>25959.8</v>
+        <v>1106.6</v>
       </c>
       <c r="V3">
-        <v>0.5917829079196026</v>
+        <v>0.244169369607908</v>
       </c>
       <c r="W3">
-        <v>0.152158592696496</v>
+        <v>0.1310291262135922</v>
       </c>
       <c r="X3">
-        <v>0.08908300212760197</v>
+        <v>0.0683979801202918</v>
       </c>
       <c r="Y3">
-        <v>0.06307559056889399</v>
+        <v>0.06263114609330042</v>
       </c>
       <c r="Z3">
-        <v>0.1463371784615962</v>
+        <v>0.3817617963413676</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06818593062433446</v>
+        <v>0.06590599169183199</v>
       </c>
       <c r="AC3">
-        <v>-0.06818593062433446</v>
+        <v>-0.06590599169183199</v>
       </c>
       <c r="AD3">
-        <v>58627.7</v>
+        <v>758.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>58627.7</v>
+        <v>758.7</v>
       </c>
       <c r="AG3">
-        <v>32667.9</v>
+        <v>-347.8999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.572006579846002</v>
+        <v>0.1433998639147199</v>
       </c>
       <c r="AI3">
-        <v>0.6542503389669737</v>
+        <v>0.2262412404950052</v>
       </c>
       <c r="AJ3">
-        <v>0.4268360880642843</v>
+        <v>-0.08314612112231724</v>
       </c>
       <c r="AK3">
-        <v>0.5132370893014531</v>
+        <v>-0.1548355512038808</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,117 +826,733 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Ahli Bank Q.P.S.C. (DSM:ABQK)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0549</v>
+      </c>
+      <c r="E4">
+        <v>0.0525</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>238.5</v>
+      </c>
+      <c r="L4">
+        <v>0.6798745724059293</v>
+      </c>
+      <c r="M4">
+        <v>187.2</v>
+      </c>
+      <c r="N4">
+        <v>0.07742896140960417</v>
+      </c>
+      <c r="O4">
+        <v>0.7849056603773584</v>
+      </c>
+      <c r="P4">
+        <v>187.2</v>
+      </c>
+      <c r="Q4">
+        <v>0.07742896140960417</v>
+      </c>
+      <c r="R4">
+        <v>0.7849056603773584</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1467.2</v>
+      </c>
+      <c r="V4">
+        <v>0.6068577573727096</v>
+      </c>
+      <c r="W4">
+        <v>0.1080456645827671</v>
+      </c>
+      <c r="X4">
+        <v>0.0756879684964183</v>
+      </c>
+      <c r="Y4">
+        <v>0.03235769608634875</v>
+      </c>
+      <c r="Z4">
+        <v>0.291192828089981</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06663416389311541</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06663416389311541</v>
+      </c>
+      <c r="AD4">
+        <v>1401.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1401.9</v>
+      </c>
+      <c r="AG4">
+        <v>-65.29999999999995</v>
+      </c>
+      <c r="AH4">
+        <v>0.3670279610430412</v>
+      </c>
+      <c r="AI4">
+        <v>0.3826146288209607</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.02775888454344498</v>
+      </c>
+      <c r="AK4">
+        <v>-0.02972505462490893</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Qatar Islamic Bank (Q.P.S.C.) (DSM:QIBK)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.103</v>
+      </c>
+      <c r="E5">
+        <v>0.0877</v>
+      </c>
+      <c r="F5">
+        <v>0.0635</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1240.2</v>
+      </c>
+      <c r="L5">
+        <v>0.4090234490946869</v>
+      </c>
+      <c r="M5">
+        <v>692.9</v>
+      </c>
+      <c r="N5">
+        <v>0.0499780007357131</v>
+      </c>
+      <c r="O5">
+        <v>0.5587002096436058</v>
+      </c>
+      <c r="P5">
+        <v>692.9</v>
+      </c>
+      <c r="Q5">
+        <v>0.0499780007357131</v>
+      </c>
+      <c r="R5">
+        <v>0.5587002096436058</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1565.6</v>
+      </c>
+      <c r="V5">
+        <v>0.1129247480903917</v>
+      </c>
+      <c r="W5">
+        <v>0.1578846863820957</v>
+      </c>
+      <c r="X5">
+        <v>0.07861475146124669</v>
+      </c>
+      <c r="Y5">
+        <v>0.07926993492084902</v>
+      </c>
+      <c r="Z5">
+        <v>0.1939898401811877</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06682969492685656</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06682969492685656</v>
+      </c>
+      <c r="AD5">
+        <v>10334.8</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>10334.8</v>
+      </c>
+      <c r="AG5">
+        <v>8769.199999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.4270772638425713</v>
+      </c>
+      <c r="AI5">
+        <v>0.5486931453175686</v>
+      </c>
+      <c r="AJ5">
+        <v>0.3874468150910384</v>
+      </c>
+      <c r="AK5">
+        <v>0.507779521358217</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Masraf Al Rayan (Q.P.S.C.) (DSM:MARK)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.119</v>
+      </c>
+      <c r="E6">
+        <v>-0.0694</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>412.7</v>
+      </c>
+      <c r="L6">
+        <v>0.167362828987388</v>
+      </c>
+      <c r="M6">
+        <v>301.9</v>
+      </c>
+      <c r="N6">
+        <v>0.0479815638906548</v>
+      </c>
+      <c r="O6">
+        <v>0.7315241095226557</v>
+      </c>
+      <c r="P6">
+        <v>301.9</v>
+      </c>
+      <c r="Q6">
+        <v>0.0479815638906548</v>
+      </c>
+      <c r="R6">
+        <v>0.7315241095226557</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1215.3</v>
+      </c>
+      <c r="V6">
+        <v>0.1931500317863954</v>
+      </c>
+      <c r="W6">
+        <v>0.06161356782419158</v>
+      </c>
+      <c r="X6">
+        <v>0.08630287004781978</v>
+      </c>
+      <c r="Y6">
+        <v>-0.0246893022236282</v>
+      </c>
+      <c r="Z6">
+        <v>0.1513490621624276</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06720184989212233</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06720184989212233</v>
+      </c>
+      <c r="AD6">
+        <v>7427.1</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>7427.1</v>
+      </c>
+      <c r="AG6">
+        <v>6211.8</v>
+      </c>
+      <c r="AH6">
+        <v>0.5413693318074801</v>
+      </c>
+      <c r="AI6">
+        <v>0.5171751074097027</v>
+      </c>
+      <c r="AJ6">
+        <v>0.4967929749356196</v>
+      </c>
+      <c r="AK6">
+        <v>0.4725383398247323</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Qatar National Bank (Q.P.S.C.) (DSM:QNBK)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0757</v>
+      </c>
+      <c r="E7">
+        <v>0.0289</v>
+      </c>
+      <c r="F7">
+        <v>0.0999</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>4490.9</v>
+      </c>
+      <c r="L7">
+        <v>0.5234454222274025</v>
+      </c>
+      <c r="M7">
+        <v>2804</v>
+      </c>
+      <c r="N7">
+        <v>0.06392034121243484</v>
+      </c>
+      <c r="O7">
+        <v>0.624373733550068</v>
+      </c>
+      <c r="P7">
+        <v>2804</v>
+      </c>
+      <c r="Q7">
+        <v>0.06392034121243484</v>
+      </c>
+      <c r="R7">
+        <v>0.624373733550068</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>25959.8</v>
+      </c>
+      <c r="V7">
+        <v>0.5917829079196026</v>
+      </c>
+      <c r="W7">
+        <v>0.152158592696496</v>
+      </c>
+      <c r="X7">
+        <v>0.08906162229806472</v>
+      </c>
+      <c r="Y7">
+        <v>0.06309697039843123</v>
+      </c>
+      <c r="Z7">
+        <v>0.1463371784615962</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06817678019796851</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06817678019796851</v>
+      </c>
+      <c r="AD7">
+        <v>58627.7</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>58627.7</v>
+      </c>
+      <c r="AG7">
+        <v>32667.9</v>
+      </c>
+      <c r="AH7">
+        <v>0.572006579846002</v>
+      </c>
+      <c r="AI7">
+        <v>0.6542503389669737</v>
+      </c>
+      <c r="AJ7">
+        <v>0.4268360880642843</v>
+      </c>
+      <c r="AK7">
+        <v>0.5132370893014531</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Doha Bank Q.P.S.C. (DSM:DHBK)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0256</v>
+      </c>
+      <c r="E8">
+        <v>-0.0178</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>228.8</v>
+      </c>
+      <c r="L8">
+        <v>0.4138929088277859</v>
+      </c>
+      <c r="M8">
+        <v>116.1</v>
+      </c>
+      <c r="N8">
+        <v>0.06846729964026656</v>
+      </c>
+      <c r="O8">
+        <v>0.5074300699300699</v>
+      </c>
+      <c r="P8">
+        <v>116.1</v>
+      </c>
+      <c r="Q8">
+        <v>0.06846729964026656</v>
+      </c>
+      <c r="R8">
+        <v>0.5074300699300699</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>900.2</v>
+      </c>
+      <c r="V8">
+        <v>0.530872206168544</v>
+      </c>
+      <c r="W8">
+        <v>0.0579475230473103</v>
+      </c>
+      <c r="X8">
+        <v>0.1795139828729171</v>
+      </c>
+      <c r="Y8">
+        <v>-0.1215664598256068</v>
+      </c>
+      <c r="Z8">
+        <v>0.04640581583741175</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06825839400315924</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06825839400315924</v>
+      </c>
+      <c r="AD8">
+        <v>10944</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>10944</v>
+      </c>
+      <c r="AG8">
+        <v>10043.8</v>
+      </c>
+      <c r="AH8">
+        <v>0.8658433348892773</v>
+      </c>
+      <c r="AI8">
+        <v>0.7273694005051177</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8555560287916861</v>
+      </c>
+      <c r="AK8">
+        <v>0.7100199352457973</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>The Commercial Bank (P.S.Q.C.) (DSM:CBQK)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D9">
         <v>0.0866</v>
       </c>
-      <c r="E4">
+      <c r="E9">
         <v>0.102</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>844.5</v>
       </c>
-      <c r="L4">
+      <c r="L9">
         <v>0.7076420311714429</v>
       </c>
-      <c r="M4">
+      <c r="M9">
         <v>355.9</v>
       </c>
-      <c r="N4">
+      <c r="N9">
         <v>0.07359387923904052</v>
       </c>
-      <c r="O4">
+      <c r="O9">
         <v>0.421432800473653</v>
       </c>
-      <c r="P4">
+      <c r="P9">
         <v>355.9</v>
       </c>
-      <c r="Q4">
+      <c r="Q9">
         <v>0.07359387923904052</v>
       </c>
-      <c r="R4">
+      <c r="R9">
         <v>0.421432800473653</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
         <v>3913.4</v>
       </c>
-      <c r="V4">
+      <c r="V9">
         <v>0.8092224979321754</v>
       </c>
-      <c r="W4">
+      <c r="W9">
         <v>0.1226811162601508</v>
       </c>
-      <c r="X4">
-        <v>0.1159571732545281</v>
-      </c>
-      <c r="Y4">
-        <v>0.006723943005622735</v>
-      </c>
-      <c r="Z4">
+      <c r="X9">
+        <v>0.1159225188097977</v>
+      </c>
+      <c r="Y9">
+        <v>0.006758597450353121</v>
+      </c>
+      <c r="Z9">
         <v>0.07708405999302408</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07019294463048451</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07019294463048451</v>
-      </c>
-      <c r="AD4">
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.07018395790797513</v>
+      </c>
+      <c r="AC9">
+        <v>-0.07018395790797513</v>
+      </c>
+      <c r="AD9">
         <v>13812.5</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
         <v>13812.5</v>
       </c>
-      <c r="AG4">
+      <c r="AG9">
         <v>9899.1</v>
       </c>
-      <c r="AH4">
+      <c r="AH9">
         <v>0.7406761937957477</v>
       </c>
-      <c r="AI4">
+      <c r="AI9">
         <v>0.6559700996362187</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ9">
         <v>0.6718040596941995</v>
       </c>
-      <c r="AK4">
+      <c r="AK9">
         <v>0.5774359512809744</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
         <v>0</v>
       </c>
     </row>
